--- a/REDCap/TEST_CLASSIC/TEST_CLASSIC_other.xlsx
+++ b/REDCap/TEST_CLASSIC/TEST_CLASSIC_other.xlsx
@@ -14,154 +14,154 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
-    <t xml:space="preserve">&amp;id=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=50</t>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=50</t>
   </si>
   <si>
     <t xml:space="preserve">record_id</t>
